--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/54.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/54.xlsx
@@ -426,13 +426,13 @@
         <v>-23.17708388850203</v>
       </c>
       <c r="E2">
-        <v>-22.45904590180687</v>
+        <v>-22.26921679987934</v>
       </c>
       <c r="F2">
-        <v>0.2853484003622407</v>
+        <v>-0.2278823630228461</v>
       </c>
       <c r="G2">
-        <v>-14.83465999432701</v>
+        <v>-15.34551027649195</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.89617446945263</v>
       </c>
       <c r="E3">
-        <v>-23.42382370371902</v>
+        <v>-22.6860673607594</v>
       </c>
       <c r="F3">
-        <v>0.4630100139754563</v>
+        <v>-0.3516164303464111</v>
       </c>
       <c r="G3">
-        <v>-15.64871321079718</v>
+        <v>-15.47126796989224</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.55416164137496</v>
       </c>
       <c r="E4">
-        <v>-23.09758790773244</v>
+        <v>-23.76268488523898</v>
       </c>
       <c r="F4">
-        <v>0.5722236290953487</v>
+        <v>-0.3667291652430853</v>
       </c>
       <c r="G4">
-        <v>-13.9103771983085</v>
+        <v>-14.65361122460258</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.14761672734253</v>
       </c>
       <c r="E5">
-        <v>-24.13144758063159</v>
+        <v>-24.23113740743645</v>
       </c>
       <c r="F5">
-        <v>0.1764752442448989</v>
+        <v>-0.1106045912367005</v>
       </c>
       <c r="G5">
-        <v>-14.31841352293306</v>
+        <v>-14.33718928195904</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.69051800332939</v>
       </c>
       <c r="E6">
-        <v>-22.89992454577163</v>
+        <v>-24.00427444507419</v>
       </c>
       <c r="F6">
-        <v>0.2681912547154574</v>
+        <v>-0.2569207823279828</v>
       </c>
       <c r="G6">
-        <v>-13.7433038965781</v>
+        <v>-14.53784972345811</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.1964774571049</v>
       </c>
       <c r="E7">
-        <v>-22.50222942994402</v>
+        <v>-25.01032928756625</v>
       </c>
       <c r="F7">
-        <v>0.1354263259665722</v>
+        <v>-0.1540574317179514</v>
       </c>
       <c r="G7">
-        <v>-13.04310696229455</v>
+        <v>-13.62626949067379</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.66865490920932</v>
       </c>
       <c r="E8">
-        <v>-25.35080260583295</v>
+        <v>-25.65632063323443</v>
       </c>
       <c r="F8">
-        <v>-0.1736897391642997</v>
+        <v>-0.2012337836747861</v>
       </c>
       <c r="G8">
-        <v>-13.70034129184221</v>
+        <v>-13.28202241277267</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.11183242987676</v>
       </c>
       <c r="E9">
-        <v>-25.87081633308175</v>
+        <v>-26.06766456972117</v>
       </c>
       <c r="F9">
-        <v>0.6490977808099484</v>
+        <v>-0.06840507063588533</v>
       </c>
       <c r="G9">
-        <v>-11.72438425218126</v>
+        <v>-13.29671130333042</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.57373900462408</v>
       </c>
       <c r="E10">
-        <v>-25.93802794430359</v>
+        <v>-26.61255320469411</v>
       </c>
       <c r="F10">
-        <v>0.04662119854945122</v>
+        <v>0.003839335664467956</v>
       </c>
       <c r="G10">
-        <v>-10.68352225027009</v>
+        <v>-12.7633294482252</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.08714130582164</v>
       </c>
       <c r="E11">
-        <v>-24.72098696932016</v>
+        <v>-26.90493412899934</v>
       </c>
       <c r="F11">
-        <v>0.2890048140781978</v>
+        <v>-0.01786140518667069</v>
       </c>
       <c r="G11">
-        <v>-12.46923382469851</v>
+        <v>-11.94055956535013</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.67278954200746</v>
       </c>
       <c r="E12">
-        <v>-26.34056852731942</v>
+        <v>-27.32950120958848</v>
       </c>
       <c r="F12">
-        <v>0.6390165495178785</v>
+        <v>0.05366729167766382</v>
       </c>
       <c r="G12">
-        <v>-11.21485818823204</v>
+        <v>-11.42427005686417</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.34557462127041</v>
       </c>
       <c r="E13">
-        <v>-27.34894194850341</v>
+        <v>-28.2948541276996</v>
       </c>
       <c r="F13">
-        <v>0.2973357050481524</v>
+        <v>0.2325142990442855</v>
       </c>
       <c r="G13">
-        <v>-11.33894736668054</v>
+        <v>-10.88965667881835</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.15381685394239</v>
       </c>
       <c r="E14">
-        <v>-27.60389503513525</v>
+        <v>-28.85378556057032</v>
       </c>
       <c r="F14">
-        <v>0.8652287766091731</v>
+        <v>0.4814486439943705</v>
       </c>
       <c r="G14">
-        <v>-10.73227003333586</v>
+        <v>-11.09311618657088</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.11221643277084</v>
       </c>
       <c r="E15">
-        <v>-28.76402214879028</v>
+        <v>-29.77669309180755</v>
       </c>
       <c r="F15">
-        <v>1.850208977316759</v>
+        <v>0.7092223436399422</v>
       </c>
       <c r="G15">
-        <v>-10.37471456236687</v>
+        <v>-10.8332813988301</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.20856286693993</v>
       </c>
       <c r="E16">
-        <v>-27.99083049672064</v>
+        <v>-30.4001688647096</v>
       </c>
       <c r="F16">
-        <v>1.36449906415488</v>
+        <v>0.5025214823541871</v>
       </c>
       <c r="G16">
-        <v>-10.75741693725216</v>
+        <v>-10.36701754398807</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.42652982958409</v>
       </c>
       <c r="E17">
-        <v>-29.88929812648228</v>
+        <v>-29.97972043123044</v>
       </c>
       <c r="F17">
-        <v>1.152226603717895</v>
+        <v>0.9579214322476322</v>
       </c>
       <c r="G17">
-        <v>-10.08401886910901</v>
+        <v>-10.04397119972045</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.76501917829101</v>
       </c>
       <c r="E18">
-        <v>-30.32965599593616</v>
+        <v>-32.19456310482695</v>
       </c>
       <c r="F18">
-        <v>2.172940917447446</v>
+        <v>0.9963609932071404</v>
       </c>
       <c r="G18">
-        <v>-9.572483304017442</v>
+        <v>-9.524559846790952</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.19434674203081</v>
       </c>
       <c r="E19">
-        <v>-30.29883293760295</v>
+        <v>-32.26001766813382</v>
       </c>
       <c r="F19">
-        <v>2.136539140298825</v>
+        <v>0.9592948654014737</v>
       </c>
       <c r="G19">
-        <v>-8.961283765466117</v>
+        <v>-8.996196778723272</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.66286295951288</v>
       </c>
       <c r="E20">
-        <v>-31.79713516896578</v>
+        <v>-31.87976623418374</v>
       </c>
       <c r="F20">
-        <v>2.380475116340417</v>
+        <v>1.337880306033321</v>
       </c>
       <c r="G20">
-        <v>-9.341986570845686</v>
+        <v>-9.091470968797957</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-20.13643074953394</v>
       </c>
       <c r="E21">
-        <v>-30.65050064361661</v>
+        <v>-32.86491990489341</v>
       </c>
       <c r="F21">
-        <v>2.226701961889134</v>
+        <v>1.511164826290144</v>
       </c>
       <c r="G21">
-        <v>-8.823035383746152</v>
+        <v>-8.983686227130365</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.59515881773497</v>
       </c>
       <c r="E22">
-        <v>-31.82399581254228</v>
+        <v>-33.75909200431496</v>
       </c>
       <c r="F22">
-        <v>2.001230295255942</v>
+        <v>1.387502826930622</v>
       </c>
       <c r="G22">
-        <v>-8.45052286803074</v>
+        <v>-9.258395295979089</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-21.00602950100463</v>
       </c>
       <c r="E23">
-        <v>-32.58319221569121</v>
+        <v>-34.42703965620933</v>
       </c>
       <c r="F23">
-        <v>2.845633234238841</v>
+        <v>1.659250410153805</v>
       </c>
       <c r="G23">
-        <v>-9.080950055074153</v>
+        <v>-8.938129809964455</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.32190181432719</v>
       </c>
       <c r="E24">
-        <v>-32.70074913669333</v>
+        <v>-34.40609319968685</v>
       </c>
       <c r="F24">
-        <v>3.134968714158263</v>
+        <v>1.434590543575357</v>
       </c>
       <c r="G24">
-        <v>-8.262450775944744</v>
+        <v>-8.541384100901578</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.52889239925769</v>
       </c>
       <c r="E25">
-        <v>-34.31576599289286</v>
+        <v>-34.44465768433617</v>
       </c>
       <c r="F25">
-        <v>2.872765580150136</v>
+        <v>1.623623984894204</v>
       </c>
       <c r="G25">
-        <v>-8.701296692630534</v>
+        <v>-8.757244912244216</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-21.62366752815715</v>
       </c>
       <c r="E26">
-        <v>-32.75364850581393</v>
+        <v>-34.78573555388289</v>
       </c>
       <c r="F26">
-        <v>2.244924388015918</v>
+        <v>1.395723545036004</v>
       </c>
       <c r="G26">
-        <v>-8.629755803526884</v>
+        <v>-9.015123167571284</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-21.59956623417781</v>
       </c>
       <c r="E27">
-        <v>-34.21483309997289</v>
+        <v>-34.28827589142929</v>
       </c>
       <c r="F27">
-        <v>2.45940361921396</v>
+        <v>1.42352189833915</v>
       </c>
       <c r="G27">
-        <v>-9.265486484524207</v>
+        <v>-8.499492457647641</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-21.44045222875252</v>
       </c>
       <c r="E28">
-        <v>-33.76986977245321</v>
+        <v>-34.83691636711758</v>
       </c>
       <c r="F28">
-        <v>2.905467868477855</v>
+        <v>1.647462742011969</v>
       </c>
       <c r="G28">
-        <v>-8.423667722616173</v>
+        <v>-8.839876128904425</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-21.16945142246949</v>
       </c>
       <c r="E29">
-        <v>-33.40237957825676</v>
+        <v>-34.3845104925663</v>
       </c>
       <c r="F29">
-        <v>2.005867495976814</v>
+        <v>1.402188124247452</v>
       </c>
       <c r="G29">
-        <v>-7.539881174906798</v>
+        <v>-8.597001265961334</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-20.81255602665102</v>
       </c>
       <c r="E30">
-        <v>-33.84470733390398</v>
+        <v>-34.92878325507419</v>
       </c>
       <c r="F30">
-        <v>2.071018592206995</v>
+        <v>1.329671185071577</v>
       </c>
       <c r="G30">
-        <v>-8.529486000233437</v>
+        <v>-8.357787866384676</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-20.3893969072001</v>
       </c>
       <c r="E31">
-        <v>-33.75215891060922</v>
+        <v>-33.87508207331042</v>
       </c>
       <c r="F31">
-        <v>2.189014558531368</v>
+        <v>1.486080204598569</v>
       </c>
       <c r="G31">
-        <v>-8.553345101934966</v>
+        <v>-8.036678191257529</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-19.90625310511888</v>
       </c>
       <c r="E32">
-        <v>-33.12235912375546</v>
+        <v>-34.04802675990036</v>
       </c>
       <c r="F32">
-        <v>2.527430807066661</v>
+        <v>1.376359628628163</v>
       </c>
       <c r="G32">
-        <v>-7.75994968962985</v>
+        <v>-8.384100082330804</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-19.4026011655461</v>
       </c>
       <c r="E33">
-        <v>-33.23505925638435</v>
+        <v>-33.57442989123017</v>
       </c>
       <c r="F33">
-        <v>1.92044956286974</v>
+        <v>1.339937970661875</v>
       </c>
       <c r="G33">
-        <v>-7.097986245779341</v>
+        <v>-8.311066137188941</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.90876420888573</v>
       </c>
       <c r="E34">
-        <v>-31.69649436261932</v>
+        <v>-32.93678225892113</v>
       </c>
       <c r="F34">
-        <v>2.49508305998734</v>
+        <v>1.104732987045788</v>
       </c>
       <c r="G34">
-        <v>-7.202867639008991</v>
+        <v>-8.998974326430719</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-18.44058380560971</v>
       </c>
       <c r="E35">
-        <v>-31.46653845250982</v>
+        <v>-33.39780581950901</v>
       </c>
       <c r="F35">
-        <v>1.567432510492703</v>
+        <v>1.506630343127219</v>
       </c>
       <c r="G35">
-        <v>-8.031798447132642</v>
+        <v>-8.426888883425883</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.99652558525074</v>
       </c>
       <c r="E36">
-        <v>-31.25813128596582</v>
+        <v>-32.98717511767848</v>
       </c>
       <c r="F36">
-        <v>1.979732504418489</v>
+        <v>1.296675654683268</v>
       </c>
       <c r="G36">
-        <v>-7.033635861586987</v>
+        <v>-8.380554488058245</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.60528425142071</v>
       </c>
       <c r="E37">
-        <v>-30.6055691245125</v>
+        <v>-32.23452688794464</v>
       </c>
       <c r="F37">
-        <v>2.003750188895258</v>
+        <v>1.21664210969439</v>
       </c>
       <c r="G37">
-        <v>-7.365104233706514</v>
+        <v>-8.613434814018277</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.27831651674213</v>
       </c>
       <c r="E38">
-        <v>-29.5516098197303</v>
+        <v>-31.28138952846921</v>
       </c>
       <c r="F38">
-        <v>1.963527981284926</v>
+        <v>1.422153435389725</v>
       </c>
       <c r="G38">
-        <v>-8.426822672515099</v>
+        <v>-8.80855174701184</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.01125693555475</v>
       </c>
       <c r="E39">
-        <v>-30.24800760957786</v>
+        <v>-30.80578428157663</v>
       </c>
       <c r="F39">
-        <v>2.333390713165294</v>
+        <v>1.456033662164225</v>
       </c>
       <c r="G39">
-        <v>-7.506209616226871</v>
+        <v>-8.343953096576062</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-16.7852464907015</v>
       </c>
       <c r="E40">
-        <v>-30.06883853546438</v>
+        <v>-31.2784279064682</v>
       </c>
       <c r="F40">
-        <v>1.212619557586396</v>
+        <v>1.738719008573973</v>
       </c>
       <c r="G40">
-        <v>-7.071111237091537</v>
+        <v>-9.03767129323926</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-16.61264257663145</v>
       </c>
       <c r="E41">
-        <v>-29.77874675477003</v>
+        <v>-30.85258153197189</v>
       </c>
       <c r="F41">
-        <v>1.773208913756934</v>
+        <v>1.79703938720067</v>
       </c>
       <c r="G41">
-        <v>-6.972562917478512</v>
+        <v>-8.83145410105252</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-16.48736958107862</v>
       </c>
       <c r="E42">
-        <v>-28.32442506296968</v>
+        <v>-29.70504584029519</v>
       </c>
       <c r="F42">
-        <v>2.151353662930491</v>
+        <v>1.768987553472267</v>
       </c>
       <c r="G42">
-        <v>-8.017212183486613</v>
+        <v>-8.744337095186598</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-16.39189610770659</v>
       </c>
       <c r="E43">
-        <v>-28.81369498018041</v>
+        <v>-29.64919390612159</v>
       </c>
       <c r="F43">
-        <v>1.786485986489004</v>
+        <v>1.824900696426428</v>
       </c>
       <c r="G43">
-        <v>-8.588784491932863</v>
+        <v>-8.301965447501486</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-16.30335667958891</v>
       </c>
       <c r="E44">
-        <v>-29.19870584031255</v>
+        <v>-29.32646767749095</v>
       </c>
       <c r="F44">
-        <v>2.561475050586915</v>
+        <v>1.605727935524124</v>
       </c>
       <c r="G44">
-        <v>-7.586298333912919</v>
+        <v>-9.283101897338669</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-16.23225026958963</v>
       </c>
       <c r="E45">
-        <v>-27.72706499966987</v>
+        <v>-28.37003132470094</v>
       </c>
       <c r="F45">
-        <v>2.177907808394632</v>
+        <v>2.122846227130549</v>
       </c>
       <c r="G45">
-        <v>-7.258176923333594</v>
+        <v>-9.347184127342341</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.17282514153354</v>
       </c>
       <c r="E46">
-        <v>-26.55078481922948</v>
+        <v>-27.70884694873702</v>
       </c>
       <c r="F46">
-        <v>2.790420890107448</v>
+        <v>1.684219060408988</v>
       </c>
       <c r="G46">
-        <v>-7.583596928752874</v>
+        <v>-9.67243198439358</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.11186919389611</v>
       </c>
       <c r="E47">
-        <v>-26.11743249906547</v>
+        <v>-27.49091413711788</v>
       </c>
       <c r="F47">
-        <v>2.608652230911153</v>
+        <v>2.073444051962392</v>
       </c>
       <c r="G47">
-        <v>-8.290203079200456</v>
+        <v>-9.515230729461287</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.03944649416371</v>
       </c>
       <c r="E48">
-        <v>-25.7531846922585</v>
+        <v>-28.22401520879761</v>
       </c>
       <c r="F48">
-        <v>2.412688667900485</v>
+        <v>2.014111408369474</v>
       </c>
       <c r="G48">
-        <v>-8.744347026823215</v>
+        <v>-9.690424799399517</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.97534783384545</v>
       </c>
       <c r="E49">
-        <v>-26.08469616046402</v>
+        <v>-26.61216375592945</v>
       </c>
       <c r="F49">
-        <v>2.629732524577594</v>
+        <v>1.891741662158321</v>
       </c>
       <c r="G49">
-        <v>-7.702707046710311</v>
+        <v>-9.928807252045818</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.92420042403445</v>
       </c>
       <c r="E50">
-        <v>-25.68689688973422</v>
+        <v>-26.64164412171938</v>
       </c>
       <c r="F50">
-        <v>2.773237236703775</v>
+        <v>1.96797962770757</v>
       </c>
       <c r="G50">
-        <v>-9.168265693672431</v>
+        <v>-10.17138747643591</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.88019610627949</v>
       </c>
       <c r="E51">
-        <v>-25.30078108194422</v>
+        <v>-25.23516349357308</v>
       </c>
       <c r="F51">
-        <v>2.795676052910808</v>
+        <v>2.040382252181858</v>
       </c>
       <c r="G51">
-        <v>-9.273746295644688</v>
+        <v>-10.41666579544052</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.84790515916788</v>
       </c>
       <c r="E52">
-        <v>-25.85149786296503</v>
+        <v>-25.93768378027901</v>
       </c>
       <c r="F52">
-        <v>2.501307412651976</v>
+        <v>1.813898320582445</v>
       </c>
       <c r="G52">
-        <v>-10.42524341893277</v>
+        <v>-10.34969345918106</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.84918950559276</v>
       </c>
       <c r="E53">
-        <v>-23.85850739524129</v>
+        <v>-25.48769384661081</v>
       </c>
       <c r="F53">
-        <v>2.75336304597581</v>
+        <v>1.858691459521426</v>
       </c>
       <c r="G53">
-        <v>-8.579276605144075</v>
+        <v>-10.48073809380757</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.88991082740793</v>
       </c>
       <c r="E54">
-        <v>-25.28179319043006</v>
+        <v>-24.78714344609822</v>
       </c>
       <c r="F54">
-        <v>2.919674369435866</v>
+        <v>1.983702041012705</v>
       </c>
       <c r="G54">
-        <v>-9.62150917290851</v>
+        <v>-10.77443645186955</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.95817398583831</v>
       </c>
       <c r="E55">
-        <v>-24.89337691784415</v>
+        <v>-25.03491437295389</v>
       </c>
       <c r="F55">
-        <v>2.753851782743461</v>
+        <v>1.802829675346238</v>
       </c>
       <c r="G55">
-        <v>-9.976614840178433</v>
+        <v>-10.53742456507651</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.05829094539483</v>
       </c>
       <c r="E56">
-        <v>-22.9151990885995</v>
+        <v>-23.87336078998645</v>
       </c>
       <c r="F56">
-        <v>2.898980094979129</v>
+        <v>2.091648254006314</v>
       </c>
       <c r="G56">
-        <v>-10.61164037497589</v>
+        <v>-11.03445331961499</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.20128147427904</v>
       </c>
       <c r="E57">
-        <v>-24.09997468627829</v>
+        <v>-23.74750544036527</v>
       </c>
       <c r="F57">
-        <v>2.750268265358951</v>
+        <v>2.041349785308328</v>
       </c>
       <c r="G57">
-        <v>-8.611071084503237</v>
+        <v>-10.83689982510452</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.38395755025458</v>
       </c>
       <c r="E58">
-        <v>-22.4712863670496</v>
+        <v>-23.38652266331784</v>
       </c>
       <c r="F58">
-        <v>2.441873708235917</v>
+        <v>1.933519543751111</v>
       </c>
       <c r="G58">
-        <v>-9.094791445973845</v>
+        <v>-10.88637923873447</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.58263862295856</v>
       </c>
       <c r="E59">
-        <v>-24.20628514208235</v>
+        <v>-23.69169199822073</v>
       </c>
       <c r="F59">
-        <v>2.290764583352037</v>
+        <v>2.048291504143788</v>
       </c>
       <c r="G59">
-        <v>-9.979435424977892</v>
+        <v>-11.20801529060236</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.79983660384844</v>
       </c>
       <c r="E60">
-        <v>-22.31848659708279</v>
+        <v>-23.54152780012639</v>
       </c>
       <c r="F60">
-        <v>2.324429434601809</v>
+        <v>1.871844277143076</v>
       </c>
       <c r="G60">
-        <v>-10.81543093728235</v>
+        <v>-11.65822299957893</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.03650480325525</v>
       </c>
       <c r="E61">
-        <v>-22.65239362803836</v>
+        <v>-23.3898103354474</v>
       </c>
       <c r="F61">
-        <v>2.734845721053629</v>
+        <v>2.255575536081114</v>
       </c>
       <c r="G61">
-        <v>-10.07810623477587</v>
+        <v>-11.55700969080679</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.28264486506018</v>
       </c>
       <c r="E62">
-        <v>-22.81725725276161</v>
+        <v>-23.36265307682341</v>
       </c>
       <c r="F62">
-        <v>2.919301604104606</v>
+        <v>1.910966412842491</v>
       </c>
       <c r="G62">
-        <v>-10.76674936512737</v>
+        <v>-11.73877519364048</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.51086573834247</v>
       </c>
       <c r="E63">
-        <v>-23.08707279108663</v>
+        <v>-23.13929062486907</v>
       </c>
       <c r="F63">
-        <v>2.485182412789081</v>
+        <v>2.022245976264966</v>
       </c>
       <c r="G63">
-        <v>-8.718690298893865</v>
+        <v>-11.7299592108694</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.72561802234765</v>
       </c>
       <c r="E64">
-        <v>-22.28404755225446</v>
+        <v>-22.93788221490393</v>
       </c>
       <c r="F64">
-        <v>2.602348354975848</v>
+        <v>1.984606618216562</v>
       </c>
       <c r="G64">
-        <v>-10.99839485760125</v>
+        <v>-11.57859775826838</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.92658941641942</v>
       </c>
       <c r="E65">
-        <v>-23.15981819754584</v>
+        <v>-21.97190889585375</v>
       </c>
       <c r="F65">
-        <v>2.822216944496504</v>
+        <v>1.997383357037341</v>
       </c>
       <c r="G65">
-        <v>-9.848394100896922</v>
+        <v>-11.36457761024558</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.1047332972092</v>
       </c>
       <c r="E66">
-        <v>-22.18596533372233</v>
+        <v>-23.18066729187716</v>
       </c>
       <c r="F66">
-        <v>2.612512423008198</v>
+        <v>2.016251909738309</v>
       </c>
       <c r="G66">
-        <v>-9.94142705164152</v>
+        <v>-12.06699923113152</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.2379659162303</v>
       </c>
       <c r="E67">
-        <v>-21.98471542034745</v>
+        <v>-22.70451636386665</v>
       </c>
       <c r="F67">
-        <v>2.626210306380891</v>
+        <v>1.779759643178272</v>
       </c>
       <c r="G67">
-        <v>-9.951587115901543</v>
+        <v>-11.43029524974565</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.33683984177279</v>
       </c>
       <c r="E68">
-        <v>-20.84998851740144</v>
+        <v>-22.36413361508011</v>
       </c>
       <c r="F68">
-        <v>2.513035438340811</v>
+        <v>1.78081829671905</v>
       </c>
       <c r="G68">
-        <v>-10.13372008929009</v>
+        <v>-11.79304165612021</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.40427468511226</v>
       </c>
       <c r="E69">
-        <v>-21.41430430586728</v>
+        <v>-22.44190562768784</v>
       </c>
       <c r="F69">
-        <v>2.425990591654639</v>
+        <v>2.091306966636361</v>
       </c>
       <c r="G69">
-        <v>-10.67360716637997</v>
+        <v>-12.55174917226484</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.4344702147169</v>
       </c>
       <c r="E70">
-        <v>-22.43902098974495</v>
+        <v>-22.1991748924027</v>
       </c>
       <c r="F70">
-        <v>2.428848459194298</v>
+        <v>2.000945336869379</v>
       </c>
       <c r="G70">
-        <v>-11.10028682820894</v>
+        <v>-11.39688191361778</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.412105339149</v>
       </c>
       <c r="E71">
-        <v>-23.36325536386643</v>
+        <v>-21.90072128445318</v>
       </c>
       <c r="F71">
-        <v>2.726026921683426</v>
+        <v>1.815743923155883</v>
       </c>
       <c r="G71">
-        <v>-10.36969577532934</v>
+        <v>-11.6486522124249</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.35464620145837</v>
       </c>
       <c r="E72">
-        <v>-22.74424919480995</v>
+        <v>-21.78382778489318</v>
       </c>
       <c r="F72">
-        <v>2.276543171780775</v>
+        <v>1.485395973123857</v>
       </c>
       <c r="G72">
-        <v>-10.69104049918977</v>
+        <v>-11.40370163742868</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.26874499120139</v>
       </c>
       <c r="E73">
-        <v>-21.68906946628268</v>
+        <v>-22.43951459341179</v>
       </c>
       <c r="F73">
-        <v>2.468051774899187</v>
+        <v>1.640254288872807</v>
       </c>
       <c r="G73">
-        <v>-10.47945029159279</v>
+        <v>-11.2738984573794</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.1521126487639</v>
       </c>
       <c r="E74">
-        <v>-22.47340116441119</v>
+        <v>-22.51374081087151</v>
       </c>
       <c r="F74">
-        <v>2.211812886191216</v>
+        <v>1.539110628990988</v>
       </c>
       <c r="G74">
-        <v>-10.1212194693338</v>
+        <v>-11.40993208413359</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.99539810792016</v>
       </c>
       <c r="E75">
-        <v>-22.55779380601813</v>
+        <v>-21.80032954417713</v>
       </c>
       <c r="F75">
-        <v>2.171965100646948</v>
+        <v>1.612301859232741</v>
       </c>
       <c r="G75">
-        <v>-10.42370732580255</v>
+        <v>-11.13274672722149</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.82088396074258</v>
       </c>
       <c r="E76">
-        <v>-24.04948220109276</v>
+        <v>-22.99721428135242</v>
       </c>
       <c r="F76">
-        <v>2.582300207093295</v>
+        <v>1.755466940723774</v>
       </c>
       <c r="G76">
-        <v>-10.53447155845548</v>
+        <v>-11.22624315434159</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.63598098286931</v>
       </c>
       <c r="E77">
-        <v>-23.11873135287425</v>
+        <v>-23.03852302125039</v>
       </c>
       <c r="F77">
-        <v>2.349757596309806</v>
+        <v>1.552934424208906</v>
       </c>
       <c r="G77">
-        <v>-10.9422049681632</v>
+        <v>-12.05013531215447</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.43829009597892</v>
       </c>
       <c r="E78">
-        <v>-25.52815576186935</v>
+        <v>-23.07397644425645</v>
       </c>
       <c r="F78">
-        <v>2.00540195349644</v>
+        <v>1.446575363159061</v>
       </c>
       <c r="G78">
-        <v>-9.660927838644611</v>
+        <v>-11.18811891191134</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.22120367670117</v>
       </c>
       <c r="E79">
-        <v>-24.79619133716554</v>
+        <v>-23.87415780141179</v>
       </c>
       <c r="F79">
-        <v>1.912374637427251</v>
+        <v>1.427604092900146</v>
       </c>
       <c r="G79">
-        <v>-9.487928660398918</v>
+        <v>-11.03820416771099</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.0090261296414</v>
       </c>
       <c r="E80">
-        <v>-24.64436518911038</v>
+        <v>-24.3904536515003</v>
       </c>
       <c r="F80">
-        <v>1.952008704181596</v>
+        <v>1.685859227866531</v>
       </c>
       <c r="G80">
-        <v>-9.63031522404297</v>
+        <v>-11.20034806713341</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.80758957487553</v>
       </c>
       <c r="E81">
-        <v>-25.47866859791353</v>
+        <v>-24.16895240236312</v>
       </c>
       <c r="F81">
-        <v>2.501709999209736</v>
+        <v>1.431235655594019</v>
       </c>
       <c r="G81">
-        <v>-9.529227716001325</v>
+        <v>-11.14950470874128</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.61132178319183</v>
       </c>
       <c r="E82">
-        <v>-26.19966505857075</v>
+        <v>-24.77718533175535</v>
       </c>
       <c r="F82">
-        <v>1.862404202220773</v>
+        <v>1.371468947482035</v>
       </c>
       <c r="G82">
-        <v>-10.11978269256976</v>
+        <v>-10.72152400251538</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.41704044237056</v>
       </c>
       <c r="E83">
-        <v>-26.05254852348357</v>
+        <v>-26.44634009471658</v>
       </c>
       <c r="F83">
-        <v>2.172407448840043</v>
+        <v>1.265701340757788</v>
       </c>
       <c r="G83">
-        <v>-9.470733686867943</v>
+        <v>-10.73716633018844</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.24618655499897</v>
       </c>
       <c r="E84">
-        <v>-27.6623757484703</v>
+        <v>-27.30278321294322</v>
       </c>
       <c r="F84">
-        <v>2.265583871041737</v>
+        <v>1.226597429141235</v>
       </c>
       <c r="G84">
-        <v>-9.850569129316222</v>
+        <v>-10.26828383382484</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.10319148600277</v>
       </c>
       <c r="E85">
-        <v>-27.86372528827335</v>
+        <v>-27.6564117482022</v>
       </c>
       <c r="F85">
-        <v>1.950492791834473</v>
+        <v>1.1422265524313</v>
       </c>
       <c r="G85">
-        <v>-9.172893836336332</v>
+        <v>-10.1309392310371</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-15.97930422987118</v>
       </c>
       <c r="E86">
-        <v>-28.57424738855084</v>
+        <v>-27.97054746164029</v>
       </c>
       <c r="F86">
-        <v>1.913582397100532</v>
+        <v>1.248685017569481</v>
       </c>
       <c r="G86">
-        <v>-9.654694081394164</v>
+        <v>-9.662401031409587</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-15.87837624692777</v>
       </c>
       <c r="E87">
-        <v>-30.35744724092123</v>
+        <v>-29.55619263542606</v>
       </c>
       <c r="F87">
-        <v>1.175565026924369</v>
+        <v>0.7368881581586401</v>
       </c>
       <c r="G87">
-        <v>-8.813302379860696</v>
+        <v>-10.1509018206389</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-15.82039377243606</v>
       </c>
       <c r="E88">
-        <v>-31.08892259043221</v>
+        <v>-30.42565058795076</v>
       </c>
       <c r="F88">
-        <v>1.628297633780799</v>
+        <v>1.174387088477588</v>
       </c>
       <c r="G88">
-        <v>-8.444481122421571</v>
+        <v>-10.20602571441331</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-15.8105047515604</v>
       </c>
       <c r="E89">
-        <v>-34.15503233646461</v>
+        <v>-30.94853083924641</v>
       </c>
       <c r="F89">
-        <v>1.970837495247229</v>
+        <v>0.959876379318239</v>
       </c>
       <c r="G89">
-        <v>-8.477265454896974</v>
+        <v>-9.529227716001325</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-15.8367797776582</v>
       </c>
       <c r="E90">
-        <v>-33.52777755200316</v>
+        <v>-32.25735718965431</v>
       </c>
       <c r="F90">
-        <v>1.504431856040189</v>
+        <v>0.8118703187252457</v>
       </c>
       <c r="G90">
-        <v>-8.83653909900084</v>
+        <v>-9.58970807245827</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-15.9083658862909</v>
       </c>
       <c r="E91">
-        <v>-33.75767459195056</v>
+        <v>-33.43358076416961</v>
       </c>
       <c r="F91">
-        <v>1.666255084911878</v>
+        <v>0.5858403324625671</v>
       </c>
       <c r="G91">
-        <v>-7.110268369730036</v>
+        <v>-9.630652899687977</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.04018106007862</v>
       </c>
       <c r="E92">
-        <v>-36.71926942212293</v>
+        <v>-35.06743607224104</v>
       </c>
       <c r="F92">
-        <v>2.063906229686558</v>
+        <v>0.5667091872949124</v>
       </c>
       <c r="G92">
-        <v>-7.802036655070604</v>
+        <v>-9.494430571838047</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.23382195599815</v>
       </c>
       <c r="E93">
-        <v>-37.62021385442295</v>
+        <v>-37.06730529198243</v>
       </c>
       <c r="F93">
-        <v>1.280936674030077</v>
+        <v>0.5068455601968006</v>
       </c>
       <c r="G93">
-        <v>-8.167322249873788</v>
+        <v>-9.266370400183193</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.46913322410071</v>
       </c>
       <c r="E94">
-        <v>-37.88438691413441</v>
+        <v>-38.89977041308227</v>
       </c>
       <c r="F94">
-        <v>1.449085316389543</v>
+        <v>0.3518141156606647</v>
       </c>
       <c r="G94">
-        <v>-7.672667156486965</v>
+        <v>-9.897714608340983</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-16.75543302262918</v>
       </c>
       <c r="E95">
-        <v>-38.99573557001582</v>
+        <v>-40.10440789775869</v>
       </c>
       <c r="F95">
-        <v>0.6658225186724704</v>
+        <v>0.2385000818969147</v>
       </c>
       <c r="G95">
-        <v>-7.835310948285819</v>
+        <v>-9.477917570688161</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.10084982757161</v>
       </c>
       <c r="E96">
-        <v>-42.25366015382811</v>
+        <v>-42.00841385123171</v>
       </c>
       <c r="F96">
-        <v>0.6114923858250593</v>
+        <v>-0.2338192721987102</v>
       </c>
       <c r="G96">
-        <v>-8.055637685560935</v>
+        <v>-9.487021570921156</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.49278027536637</v>
       </c>
       <c r="E97">
-        <v>-44.84743194696446</v>
+        <v>-43.41338649753347</v>
       </c>
       <c r="F97">
-        <v>1.019644744165029</v>
+        <v>-0.1158904036339642</v>
       </c>
       <c r="G97">
-        <v>-8.053376582957613</v>
+        <v>-9.366653445658796</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.91467959738592</v>
       </c>
       <c r="E98">
-        <v>-47.17203124508488</v>
+        <v>-45.33574635615957</v>
       </c>
       <c r="F98">
-        <v>-0.4527418661453692</v>
+        <v>-0.6122912264963736</v>
       </c>
       <c r="G98">
-        <v>-7.693894374484771</v>
+        <v>-9.598997463241465</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.3572109144323</v>
       </c>
       <c r="E99">
-        <v>-48.53109308977837</v>
+        <v>-46.59696259508782</v>
       </c>
       <c r="F99">
-        <v>-0.08848966668416214</v>
+        <v>-0.4235137507049914</v>
       </c>
       <c r="G99">
-        <v>-7.452270897755525</v>
+        <v>-9.647288391022814</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.84139453001452</v>
       </c>
       <c r="E100">
-        <v>-49.32764147866106</v>
+        <v>-49.07679911430969</v>
       </c>
       <c r="F100">
-        <v>0.1261386706463842</v>
+        <v>-0.8331381179197357</v>
       </c>
       <c r="G100">
-        <v>-8.697519360170224</v>
+        <v>-9.710609195552454</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.31711569633901</v>
       </c>
       <c r="E101">
-        <v>-51.14668646703917</v>
+        <v>-50.4193444821787</v>
       </c>
       <c r="F101">
-        <v>-0.1804293363534765</v>
+        <v>-0.7911663983546904</v>
       </c>
       <c r="G101">
-        <v>-8.039515328784685</v>
+        <v>-9.731631159726826</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.82099425372041</v>
       </c>
       <c r="E102">
-        <v>-52.76109990407718</v>
+        <v>-53.29356580272857</v>
       </c>
       <c r="F102">
-        <v>-0.7750612793094623</v>
+        <v>-1.217907321213481</v>
       </c>
       <c r="G102">
-        <v>-8.4184602344829</v>
+        <v>-10.0573292509714</v>
       </c>
     </row>
   </sheetData>
